--- a/Result/profitability/6160.xlsx
+++ b/Result/profitability/6160.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.76</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.11</v>
+        <v>-0.14875</v>
       </c>
       <c r="N2" t="n">
-        <v>41.08</v>
+        <v>41.055</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10125</v>
+        <v>0.02750000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>43.80374999999999</v>
+        <v>43.32875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2025</v>
+        <v>0.15375</v>
       </c>
       <c r="N4" t="n">
-        <v>44.7925</v>
+        <v>44.1325</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.07</v>
       </c>
       <c r="M5" t="n">
-        <v>0.35375</v>
+        <v>0.3125</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>45.7475</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4475</v>
+        <v>0.4075</v>
       </c>
       <c r="N6" t="n">
-        <v>46.91875</v>
+        <v>46.74375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.50875</v>
+        <v>0.5225000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>49.20875</v>
+        <v>49.19499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>0.63375</v>
+        <v>0.60375</v>
       </c>
       <c r="N8" t="n">
-        <v>50.82</v>
+        <v>51.07625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.53</v>
       </c>
       <c r="M10" t="n">
-        <v>0.70625</v>
+        <v>0.7062500000000002</v>
       </c>
       <c r="N10" t="n">
         <v>51.60875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>250</v>
+      </c>
+      <c r="D75" t="n">
+        <v>158</v>
+      </c>
+      <c r="E75" t="n">
+        <v>92</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-14.37%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.27125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.295</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.827586206896552</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.050000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05873925501432686</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.019999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05183474467539118</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
